--- a/strategy/IG_Engagement_Tracker.xlsx
+++ b/strategy/IG_Engagement_Tracker.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -196,8 +196,32 @@
       <color rgb="002E7D32"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="003D3530"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0027508A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00B58A00"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -257,6 +281,12 @@
         <fgColor rgb="00E8F0DE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1FA"/>
+        <bgColor rgb="00EAF1FA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -300,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -419,6 +449,19 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -845,9 +888,9 @@
           <t>Date:</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
+      <c r="B2" s="50" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
         </is>
       </c>
     </row>
@@ -921,212 +964,180 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="109.95" customHeight="1" s="36">
+    <row r="6" ht="90" customHeight="1" s="36">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>1. Peer</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="46" t="inlineStr">
         <is>
           <t>@laurenfoisy.journal</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>79.9K</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>(not tagged in email)</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>"Disappear in May and get 6 months ahead… not by doing more. By finally having a plan you can actually follow." (6-step game plan)</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Peer with adjacent voice — habits/self-improvement creator using the same "weekly reset + repeatable week" frame SAMA reduces to one screen. Big enough that her audience overlaps Sharda's buyer (women restarting their planning system in May). Quote-and-react has a clear opening on a fresh post still in the algo push.</t>
-        </is>
-      </c>
-      <c r="G6" s="32" t="inlineStr">
+      <c r="C6" s="46" t="inlineStr">
+        <is>
+          <t>81.3K</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>(re-sent in IG-PICKS — was Peer bucket on 2026-05-03)</t>
+        </is>
+      </c>
+      <c r="E6" s="46" t="inlineStr">
+        <is>
+          <t>"Your Game Plan🫶 Disappear in May and get 6 months ahead — not by doing more. By finally having a plan you can actually follow."</t>
+        </is>
+      </c>
+      <c r="F6" s="46" t="inlineStr">
+        <is>
+          <t>Habits/self-improvement creator (81.3K, +1.4K since yesterday). 6-step framework post — targets, baseline habits, repeatable week, environment, tracking, weekly reset. The line "Build a week you can actually repeat" is essentially the SAMA pitch. ⚠ Already engaged 2026-05-03 — duplicate URL from yesterday's email; picker isn't deduping.</t>
+        </is>
+      </c>
+      <c r="G6" s="51" t="inlineStr">
         <is>
           <t>https://www.instagram.com/p/DX29iSTjqCI/</t>
         </is>
       </c>
-      <c r="H6" s="33" t="inlineStr">
-        <is>
-          <t>"Build a week you can actually repeat" is the line I needed — I keep designing my dream week instead of my normal-Tuesday one. How do you decide which 3 habits make the cut?</t>
-        </is>
-      </c>
-      <c r="I6" s="44" t="inlineStr">
-        <is>
-          <t>"Build a week you can actually repeat" is the line I needed — I keep designing my dream week instead of my normal-Tuesday one. How do you decide which 3 habits make the cut?</t>
-        </is>
-      </c>
-      <c r="J6" s="45" t="inlineStr">
-        <is>
-          <t>Strong — quoted "Build a week you can actually repeat" verbatim from her caption, named the dream-week-vs-normal-Tuesday tension, and asked a specific "which 3 habits" question. Used the suggested comment verbatim — framing held up and pulled 2 likes inside 10h.</t>
-        </is>
-      </c>
-      <c r="K6" s="46" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="L6" s="46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="n"/>
-    </row>
-    <row r="7" ht="109.95" customHeight="1" s="36">
+      <c r="H6" s="52" t="inlineStr">
+        <is>
+          <t>✅ Already commented 2026-05-03 — no new suggestion (would duplicate). Existing comment was strong: "'Build a week you can actually repeat' is the line I needed — I keep designing my dream week instead of my normal-Tuesday one. How do you decide which 3 habits make the cut?"</t>
+        </is>
+      </c>
+      <c r="I6" s="46" t="n"/>
+      <c r="J6" s="53" t="n"/>
+      <c r="K6" s="46" t="n"/>
+      <c r="L6" s="46" t="n"/>
+      <c r="M6" s="46" t="n"/>
+    </row>
+    <row r="7" ht="90" customHeight="1" s="36">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>2. Dream customer</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>(no candidate this batch)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="34" t="inlineStr">
-        <is>
-          <t>No candidate this batch — both URLs in the email are 80K+ creators, not 300–5K dream-customer accounts.</t>
-        </is>
-      </c>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="29" t="n"/>
-      <c r="I7" s="22" t="n"/>
-      <c r="J7" s="24" t="n"/>
-      <c r="K7" s="14" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="14" t="n"/>
-    </row>
-    <row r="8" ht="109.95" customHeight="1" s="36">
+      <c r="C7" s="46" t="n"/>
+      <c r="D7" s="46" t="n"/>
+      <c r="E7" s="46" t="n"/>
+      <c r="F7" s="54" t="inlineStr">
+        <is>
+          <t>No candidate — both URLs are creators &gt;80K, well above the 300–5K dream-customer band. Picker also re-sent yesterday's URLs.</t>
+        </is>
+      </c>
+      <c r="G7" s="46" t="n"/>
+      <c r="H7" s="53" t="n"/>
+      <c r="I7" s="46" t="n"/>
+      <c r="J7" s="53" t="n"/>
+      <c r="K7" s="46" t="n"/>
+      <c r="L7" s="46" t="n"/>
+      <c r="M7" s="46" t="n"/>
+    </row>
+    <row r="8" ht="90" customHeight="1" s="36">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>3. Micro-influencer</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>(no candidate this batch)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="34" t="inlineStr">
-        <is>
-          <t>No candidate this batch — both creators sit above the 10K–50K micro band (79.9K and 207K). Skipped rather than padded.</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="22" t="n"/>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14" t="n"/>
-    </row>
-    <row r="9" ht="109.95" customHeight="1" s="36">
+      <c r="C8" s="46" t="n"/>
+      <c r="D8" s="46" t="n"/>
+      <c r="E8" s="46" t="n"/>
+      <c r="F8" s="54" t="inlineStr">
+        <is>
+          <t>No candidate — Lauren 81.3K (above), Jess 207K (above). Neither in the 10–50K micro band.</t>
+        </is>
+      </c>
+      <c r="G8" s="46" t="n"/>
+      <c r="H8" s="53" t="n"/>
+      <c r="I8" s="46" t="n"/>
+      <c r="J8" s="53" t="n"/>
+      <c r="K8" s="46" t="n"/>
+      <c r="L8" s="46" t="n"/>
+      <c r="M8" s="46" t="n"/>
+    </row>
+    <row r="9" ht="90" customHeight="1" s="36">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>4. Fresh post</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
+        <is>
+          <t>(no candidate this batch)</t>
+        </is>
+      </c>
+      <c r="C9" s="46" t="n"/>
+      <c r="D9" s="46" t="n"/>
+      <c r="E9" s="46" t="n"/>
+      <c r="F9" s="54" t="inlineStr">
+        <is>
+          <t>No candidate — both posts are now ~1d old (timestamp "1d" on IG), past the &lt;24h fresh-post window. @theorganisedbusymum was here yesterday at 13h; moved to Aesthetic match today.</t>
+        </is>
+      </c>
+      <c r="G9" s="46" t="n"/>
+      <c r="H9" s="53" t="n"/>
+      <c r="I9" s="46" t="n"/>
+      <c r="J9" s="53" t="n"/>
+      <c r="K9" s="46" t="n"/>
+      <c r="L9" s="46" t="n"/>
+      <c r="M9" s="46" t="n"/>
+    </row>
+    <row r="10" ht="90" customHeight="1" s="36">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>5. Aesthetic match</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>@theorganisedbusymum</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>207K</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>(not tagged in email)</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="D10" s="46" t="inlineStr">
+        <is>
+          <t>(re-sent in IG-PICKS — was Fresh-post bucket on 2026-05-03 at 13h)</t>
+        </is>
+      </c>
+      <c r="E10" s="46" t="inlineStr">
         <is>
           <t>"Tried harder for years. Bought the baskets. Did the big declutters. Wrote the lists. Still felt like I was drowning. The problem was never effort. It was the lack of a system behind it."</t>
         </is>
       </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>13h old — still in fresh-post window. Verified mum-systems creator; her audience IS Sharda's dream customer (drowning-in-effort women) which makes a thoughtful comment in HER comment section a high-leverage profile-visit driver. Caption opens with a vivid emotional hook that's easy to react to specifically.</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
+      <c r="F10" s="46" t="inlineStr">
+        <is>
+          <t>Verified busy-mum-systems creator. The "bought the baskets / did the declutters / still drowning" beat is the exact woman SAMA is for; "system not effort" framing is plug-and-play marketing for SAMA. Engagement is unusually low for her size (54 likes / 53 comments at 1d) — algo distribution may be soft. ⚠ Already engaged 2026-05-03; duplicate URL.</t>
+        </is>
+      </c>
+      <c r="G10" s="51" t="inlineStr">
         <is>
           <t>https://www.instagram.com/p/DX22D-Jk15J/</t>
         </is>
       </c>
-      <c r="H9" s="33" t="inlineStr">
-        <is>
-          <t>"The problem was never effort — it was the lack of a system" hit me in the chest. What's the one system you'd say carries the most weight day-to-day?</t>
-        </is>
-      </c>
-      <c r="I9" s="47" t="inlineStr">
-        <is>
-          <t>"The problem was never effort — it was the lack of a system" hit me in the chest. What's the one system you'd say carries the most weight day-to-day?</t>
-        </is>
-      </c>
-      <c r="J9" s="45" t="inlineStr">
-        <is>
-          <t>Strong — quoted the "effort vs system" line from her caption, added a visceral reaction ("hit me in the chest"), and asked her to name her highest-leverage system. Used the suggested comment verbatim. Sits as the only thoughtful comment above the SYSTEMS-keyword chorus on her thread.</t>
-        </is>
-      </c>
-      <c r="K9" s="46" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="L9" s="46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="n"/>
-    </row>
-    <row r="10" ht="109.95" customHeight="1" s="36">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>5. Aesthetic match</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>(no candidate this batch)</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="34" t="inlineStr">
-        <is>
-          <t>No candidate this batch — neither post reads as warm/intentional/soft-girl aesthetic (one is habits-list infographic, the other is busy-mum systems carousel). No vibe match worth flagging.</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="n"/>
+      <c r="H10" s="52" t="inlineStr">
+        <is>
+          <t>✅ Already commented 2026-05-03 — no new suggestion (would duplicate). Existing comment was strong: "'The problem was never effort — it was the lack of a system' hit me in the chest. What's the one system you'd say carries the most weight day-to-day?"</t>
+        </is>
+      </c>
+      <c r="I10" s="46" t="n"/>
+      <c r="J10" s="53" t="n"/>
+      <c r="K10" s="46" t="n"/>
+      <c r="L10" s="46" t="n"/>
+      <c r="M10" s="46" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="36">
       <c r="A12" s="35" t="inlineStr">
@@ -1143,7 +1154,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
